--- a/cote-auto.xlsx
+++ b/cote-auto.xlsx
@@ -135,8 +135,8 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -1037,10 +1037,8 @@
           <t>Dernier relevé</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>aucun relevé automatique pour l'instant</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>46296</v>
       </c>
     </row>
     <row r="5">
@@ -1049,7 +1047,7 @@
           <t>Dashboard</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>https://mattchampavier-ui.github.io/cote-auto/</t>
         </is>
@@ -1057,7 +1055,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="4" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1065,7 +1063,7 @@
           <t>Fonctionnement</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Ce fichier est régénéré automatiquement à chaque relevé (chaque lundi et le 1er du mois) à partir de tout l'historique.</t>
         </is>
@@ -1073,7 +1071,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Il est aussi joint au récap mensuel par mail. Toute modification faite à la main ici sera écrasée : enregistre une copie pour annoter.</t>
         </is>
@@ -1081,7 +1079,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="4" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1089,7 +1087,7 @@
           <t>Onglets</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr"/>
+      <c r="B10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1097,7 +1095,7 @@
           <t>Analyse du mois</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Situation actuelle de chaque véhicule : score, signal, prix, tendances, offre, ventes. Indicateurs clés en haut.</t>
         </is>
@@ -1109,7 +1107,7 @@
           <t>Historique mensuel</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Une ligne par véhicule et par mois (dernier relevé du mois). Variations vs mois précédent calculées par formule.</t>
         </is>
@@ -1121,7 +1119,7 @@
           <t>Médianes par mois</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Tableau croisé véhicule × mois des prix médians (formules sur l'onglet Historique mensuel).</t>
         </is>
@@ -1133,7 +1131,7 @@
           <t>Indice base 100</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Évolution de la médiane depuis le premier mois suivi (100 = premier mois), avec graphique.</t>
         </is>
@@ -1145,7 +1143,7 @@
           <t>Relevés</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Tous les relevés bruts, y compris l'amorce manuelle de septembre 2026.</t>
         </is>
@@ -1157,7 +1155,7 @@
           <t>Annonces</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Chaque annonce suivie : en vente ou partie (≈ vendue), durée en ligne, baisse de prix.</t>
         </is>
@@ -1169,7 +1167,7 @@
           <t>Bonnes affaires</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Annonces du dernier relevé au moins 15 % sous la cote attendue pour leur kilométrage.</t>
         </is>
@@ -1181,7 +1179,7 @@
           <t>Véhicules</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Liste des véhicules suivis ou retirés et leurs critères de recherche.</t>
         </is>
@@ -1189,7 +1187,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr"/>
-      <c r="B19" s="4" t="inlineStr"/>
+      <c r="B19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1197,7 +1195,7 @@
           <t>Définitions</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr"/>
+      <c r="B20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1205,7 +1203,7 @@
           <t>Médiane</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Prix médian des annonces retenues (après filtres : pièces, épaves, autres versions, doublons, prix aberrants).</t>
         </is>
@@ -1217,7 +1215,7 @@
           <t>Cote à km réf.</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Prix attendu à un kilométrage de référence fixe (régression prix/km) : compare les mois sans biais de kilométrage.</t>
         </is>
@@ -1229,7 +1227,7 @@
           <t>Position fourchette</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>0 % = au plancher, 100 % = au plafond de prix observé (ou saisi pendant les 3 premiers mois).</t>
         </is>
@@ -1241,7 +1239,7 @@
           <t>Score</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Sur 100 : rareté 20 %, désirabilité 20 %, « dernier de » 10 %, proximité du plancher 20 %, momentum 15 %, marché 15 %.</t>
         </is>
@@ -1253,7 +1251,7 @@
           <t>Ventes</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Annonces disparues entre deux relevés. Une annonce peut aussi être retirée sans vente : c'est une estimation.</t>
         </is>
@@ -1265,7 +1263,7 @@
           <t>Avertissement</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Outil de suivi de marché, pas un conseil d'achat.</t>
         </is>
@@ -3221,7 +3219,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Citroën Saxo VTS 16V</t>
         </is>
@@ -3232,7 +3230,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Peugeot 206 RC</t>
         </is>
@@ -3243,7 +3241,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Peugeot 208 GTi 30th</t>
         </is>
@@ -3254,7 +3252,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Porsche 911 997 Carrera S</t>
         </is>
@@ -3265,7 +3263,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Porsche Boxster 986</t>
         </is>
@@ -3276,7 +3274,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Porsche Boxster 987</t>
         </is>
@@ -3287,7 +3285,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Renault Clio II RS (172/182 ch)</t>
         </is>
@@ -3298,7 +3296,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Renault Twingo 1 découvrable</t>
         </is>
@@ -3395,7 +3393,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>

--- a/cote-auto.xlsx
+++ b/cote-auto.xlsx
@@ -19,10 +19,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Analyse du mois'!$A$8:$Y$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Historique mensuel'!$A$1:$P$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Relevés'!$A$1:$P$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Annonces'!$A$1:$O$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Bonnes affaires'!$A$1:$J$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Historique mensuel'!$A$1:$P$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Relevés'!$A$1:$P$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Annonces'!$A$1:$O$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Bonnes affaires'!$A$1:$J$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Véhicules'!$A$1:$O$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -381,12 +381,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Indice base 100'!$A$5</f>
+              <f>'Indice base 100'!$A$5:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Indice base 100'!$B$5</f>
+              <f>'Indice base 100'!$B$5:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -413,12 +413,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Indice base 100'!$A$5</f>
+              <f>'Indice base 100'!$A$5:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Indice base 100'!$C$5</f>
+              <f>'Indice base 100'!$C$5:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -445,12 +445,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Indice base 100'!$A$5</f>
+              <f>'Indice base 100'!$A$5:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Indice base 100'!$D$5</f>
+              <f>'Indice base 100'!$D$5:$D$6</f>
             </numRef>
           </val>
         </ser>
@@ -477,12 +477,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Indice base 100'!$A$5</f>
+              <f>'Indice base 100'!$A$5:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Indice base 100'!$E$5</f>
+              <f>'Indice base 100'!$E$5:$E$6</f>
             </numRef>
           </val>
         </ser>
@@ -509,12 +509,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Indice base 100'!$A$5</f>
+              <f>'Indice base 100'!$A$5:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Indice base 100'!$F$5</f>
+              <f>'Indice base 100'!$F$5:$F$6</f>
             </numRef>
           </val>
         </ser>
@@ -541,12 +541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Indice base 100'!$A$5</f>
+              <f>'Indice base 100'!$A$5:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Indice base 100'!$G$5</f>
+              <f>'Indice base 100'!$G$5:$G$6</f>
             </numRef>
           </val>
         </ser>
@@ -573,12 +573,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Indice base 100'!$A$5</f>
+              <f>'Indice base 100'!$A$5:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Indice base 100'!$H$5</f>
+              <f>'Indice base 100'!$H$5:$H$6</f>
             </numRef>
           </val>
         </ser>
@@ -605,12 +605,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Indice base 100'!$A$5</f>
+              <f>'Indice base 100'!$A$5:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Indice base 100'!$I$5</f>
+              <f>'Indice base 100'!$I$5:$I$6</f>
             </numRef>
           </val>
         </ser>
@@ -697,7 +697,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3960000"/>
@@ -1512,72 +1512,76 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Peugeot 208 GTi 30th</t>
+          <t>Peugeot 206 RC</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Hot-hatch récente à tirage limité</t>
+          <t>Hot-hatch youngtimer 2000-2005</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>67.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>À surveiller</t>
+          <t>Signal d'achat</t>
         </is>
       </c>
       <c r="E9" s="12" t="n">
-        <v>15990</v>
+        <v>9650</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>12000</v>
+        <v>6500</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>24000</v>
+        <v>13500</v>
       </c>
       <c r="H9" s="13">
         <f>IF(AND(ISNUMBER(E9),ISNUMBER(F9),ISNUMBER(G9),G9&gt;F9),(E9-F9)/(G9-F9),"")</f>
         <v/>
       </c>
-      <c r="I9" s="14" t="n"/>
+      <c r="I9" s="14" t="n">
+        <v>0.421</v>
+      </c>
       <c r="J9" s="14" t="n"/>
       <c r="K9" s="14" t="n"/>
-      <c r="L9" s="12" t="n"/>
+      <c r="L9" s="12" t="n">
+        <v>9650</v>
+      </c>
       <c r="M9" s="15" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="O9" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P9" s="17" t="n"/>
       <c r="Q9" s="16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R9" s="16" t="n">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="S9" s="16" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="W9" s="16" t="n">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="X9" s="18" t="n">
-        <v>46273</v>
+        <v>46296</v>
       </c>
       <c r="Y9" s="19" t="inlineStr">
         <is>
@@ -1588,16 +1592,16 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Porsche 911 997 Carrera S</t>
+          <t>Peugeot 208 GTi 30th</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Sportive iconique</t>
+          <t>Hot-hatch récente à tirage limité</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>67.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
@@ -1605,13 +1609,13 @@
         </is>
       </c>
       <c r="E10" s="12" t="n">
-        <v>51000</v>
+        <v>15990</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>40000</v>
+        <v>12000</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>75000</v>
+        <v>24000</v>
       </c>
       <c r="H10" s="13">
         <f>IF(AND(ISNUMBER(E10),ISNUMBER(F10),ISNUMBER(G10),G10&gt;F10),(E10-F10)/(G10-F10),"")</f>
@@ -1625,7 +1629,7 @@
         <v>100000</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O10" s="16" t="n">
         <v>0</v>
@@ -1635,22 +1639,22 @@
         <v>0</v>
       </c>
       <c r="R10" s="16" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="S10" s="16" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="V10" s="16" t="n">
         <v>50</v>
       </c>
       <c r="W10" s="16" t="n">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="X10" s="18" t="n">
         <v>46273</v>
@@ -1664,16 +1668,16 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Peugeot 206 RC</t>
+          <t>Porsche 911 997 Carrera S</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Hot-hatch youngtimer 2000-2005</t>
+          <t>Sportive iconique</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>58.2</v>
+        <v>67.2</v>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
@@ -1681,13 +1685,13 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>6790</v>
+        <v>51000</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>6500</v>
+        <v>40000</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>13500</v>
+        <v>75000</v>
       </c>
       <c r="H11" s="13">
         <f>IF(AND(ISNUMBER(E11),ISNUMBER(F11),ISNUMBER(G11),G11&gt;F11),(E11-F11)/(G11-F11),"")</f>
@@ -1698,10 +1702,10 @@
       <c r="K11" s="14" t="n"/>
       <c r="L11" s="12" t="n"/>
       <c r="M11" s="15" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O11" s="16" t="n">
         <v>0</v>
@@ -1711,22 +1715,22 @@
         <v>0</v>
       </c>
       <c r="R11" s="16" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="S11" s="16" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="V11" s="16" t="n">
         <v>50</v>
       </c>
       <c r="W11" s="16" t="n">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="X11" s="18" t="n">
         <v>46273</v>
@@ -2684,7 +2688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2888,41 +2892,49 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>Peugeot 208 GTi 30th</t>
+          <t>Peugeot 206 RC</t>
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>15990</v>
+        <v>9650</v>
       </c>
       <c r="D4" s="14">
         <f>IF(AND($B4=$B3,ISNUMBER(C4),ISNUMBER(C3)),C4/C3-1,"")</f>
         <v/>
       </c>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="12" t="n"/>
-      <c r="G4" s="12" t="n"/>
+      <c r="E4" s="12" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>12125</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>9650</v>
+      </c>
       <c r="H4" s="14">
         <f>IF(AND($B4=$B3,ISNUMBER(G4),ISNUMBER(G3)),G4/G3-1,"")</f>
         <v/>
       </c>
       <c r="I4" s="16" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="J4" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="K4" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="16" t="n"/>
       <c r="L4" s="17" t="n"/>
       <c r="M4" s="16" t="n">
         <v>1</v>
       </c>
       <c r="N4" s="11" t="n">
-        <v>67.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="O4" s="20">
         <f>IF(AND($B4=$B3,ISNUMBER(N4),ISNUMBER(N3)),N4-N3,"")</f>
@@ -2930,7 +2942,7 @@
       </c>
       <c r="P4" s="10" t="inlineStr">
         <is>
-          <t>À surveiller</t>
+          <t>Signal d'achat</t>
         </is>
       </c>
     </row>
@@ -2942,11 +2954,11 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Porsche 911 997 Carrera S</t>
+          <t>Peugeot 208 GTi 30th</t>
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>51000</v>
+        <v>15990</v>
       </c>
       <c r="D5" s="14">
         <f>IF(AND($B5=$B4,ISNUMBER(C5),ISNUMBER(C4)),C5/C4-1,"")</f>
@@ -2960,7 +2972,7 @@
         <v/>
       </c>
       <c r="I5" s="16" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J5" s="16" t="n">
         <v>0</v>
@@ -2971,7 +2983,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="11" t="n">
-        <v>67.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="O5" s="20">
         <f>IF(AND($B5=$B4,ISNUMBER(N5),ISNUMBER(N4)),N5-N4,"")</f>
@@ -2991,11 +3003,11 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Porsche Boxster 986</t>
+          <t>Porsche 911 997 Carrera S</t>
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>22425</v>
+        <v>51000</v>
       </c>
       <c r="D6" s="14">
         <f>IF(AND($B6=$B5,ISNUMBER(C6),ISNUMBER(C5)),C6/C5-1,"")</f>
@@ -3009,7 +3021,7 @@
         <v/>
       </c>
       <c r="I6" s="16" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J6" s="16" t="n">
         <v>0</v>
@@ -3020,7 +3032,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="11" t="n">
-        <v>43.1</v>
+        <v>67.2</v>
       </c>
       <c r="O6" s="20">
         <f>IF(AND($B6=$B5,ISNUMBER(N6),ISNUMBER(N5)),N6-N5,"")</f>
@@ -3028,7 +3040,7 @@
       </c>
       <c r="P6" s="10" t="inlineStr">
         <is>
-          <t>Attendre</t>
+          <t>À surveiller</t>
         </is>
       </c>
     </row>
@@ -3040,11 +3052,11 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Porsche Boxster 987</t>
+          <t>Porsche Boxster 986</t>
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>43990</v>
+        <v>22425</v>
       </c>
       <c r="D7" s="14">
         <f>IF(AND($B7=$B6,ISNUMBER(C7),ISNUMBER(C6)),C7/C6-1,"")</f>
@@ -3058,7 +3070,7 @@
         <v/>
       </c>
       <c r="I7" s="16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J7" s="16" t="n">
         <v>0</v>
@@ -3069,7 +3081,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="11" t="n">
-        <v>38.3</v>
+        <v>43.1</v>
       </c>
       <c r="O7" s="20">
         <f>IF(AND($B7=$B6,ISNUMBER(N7),ISNUMBER(N6)),N7-N6,"")</f>
@@ -3089,11 +3101,11 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Renault Clio II RS (172/182 ch)</t>
+          <t>Porsche Boxster 987</t>
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>8899.5</v>
+        <v>43990</v>
       </c>
       <c r="D8" s="14">
         <f>IF(AND($B8=$B7,ISNUMBER(C8),ISNUMBER(C7)),C8/C7-1,"")</f>
@@ -3107,7 +3119,7 @@
         <v/>
       </c>
       <c r="I8" s="16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J8" s="16" t="n">
         <v>0</v>
@@ -3118,7 +3130,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="11" t="n">
-        <v>52</v>
+        <v>38.3</v>
       </c>
       <c r="O8" s="20">
         <f>IF(AND($B8=$B7,ISNUMBER(N8),ISNUMBER(N7)),N8-N7,"")</f>
@@ -3138,11 +3150,11 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Renault Twingo 1 découvrable</t>
+          <t>Renault Clio II RS (172/182 ch)</t>
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>5490</v>
+        <v>8899.5</v>
       </c>
       <c r="D9" s="14">
         <f>IF(AND($B9=$B8,ISNUMBER(C9),ISNUMBER(C8)),C9/C8-1,"")</f>
@@ -3156,7 +3168,7 @@
         <v/>
       </c>
       <c r="I9" s="16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J9" s="16" t="n">
         <v>0</v>
@@ -3167,7 +3179,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="11" t="n">
-        <v>46.5</v>
+        <v>52</v>
       </c>
       <c r="O9" s="20">
         <f>IF(AND($B9=$B8,ISNUMBER(N9),ISNUMBER(N8)),N9-N8,"")</f>
@@ -3179,9 +3191,58 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Renault Twingo 1 découvrable</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>5490</v>
+      </c>
+      <c r="D10" s="14">
+        <f>IF(AND($B10=$B9,ISNUMBER(C10),ISNUMBER(C9)),C10/C9-1,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="12" t="n"/>
+      <c r="H10" s="14">
+        <f>IF(AND($B10=$B9,ISNUMBER(G10),ISNUMBER(G9)),G10/G9-1,"")</f>
+        <v/>
+      </c>
+      <c r="I10" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="16" t="n"/>
+      <c r="L10" s="17" t="n"/>
+      <c r="M10" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="11" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="O10" s="20">
+        <f>IF(AND($B10=$B9,ISNUMBER(N10),ISNUMBER(N9)),N10-N9,"")</f>
+        <v/>
+      </c>
+      <c r="P10" s="10" t="inlineStr">
+        <is>
+          <t>Attendre</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P9"/>
-  <conditionalFormatting sqref="P2:P9">
+  <autoFilter ref="A1:P10"/>
+  <conditionalFormatting sqref="P2:P10">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>ISNUMBER(SEARCH("achat",P2))</formula>
     </cfRule>
@@ -3199,11 +3260,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3217,6 +3279,11 @@
           <t>2026-09</t>
         </is>
       </c>
+      <c r="C1" s="21" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -3225,7 +3292,11 @@
         </is>
       </c>
       <c r="B2" s="22">
-        <f>IFERROR(AVERAGEIFS('Historique mensuel'!$C$2:$C$9,'Historique mensuel'!$B$2:$B$9,$A2,'Historique mensuel'!$A$2:$A$9,B$1),"")</f>
+        <f>IFERROR(AVERAGEIFS('Historique mensuel'!$C$2:$C$10,'Historique mensuel'!$B$2:$B$10,$A2,'Historique mensuel'!$A$2:$A$10,B$1),"")</f>
+        <v/>
+      </c>
+      <c r="C2" s="22">
+        <f>IFERROR(AVERAGEIFS('Historique mensuel'!$C$2:$C$10,'Historique mensuel'!$B$2:$B$10,$A2,'Historique mensuel'!$A$2:$A$10,C$1),"")</f>
         <v/>
       </c>
     </row>
@@ -3236,7 +3307,11 @@
         </is>
       </c>
       <c r="B3" s="22">
-        <f>IFERROR(AVERAGEIFS('Historique mensuel'!$C$2:$C$9,'Historique mensuel'!$B$2:$B$9,$A3,'Historique mensuel'!$A$2:$A$9,B$1),"")</f>
+        <f>IFERROR(AVERAGEIFS('Historique mensuel'!$C$2:$C$10,'Historique mensuel'!$B$2:$B$10,$A3,'Historique mensuel'!$A$2:$A$10,B$1),"")</f>
+        <v/>
+      </c>
+      <c r="C3" s="22">
+        <f>IFERROR(AVERAGEIFS('Historique mensuel'!$C$2:$C$10,'Historique mensuel'!$B$2:$B$10,$A3,'Historique mensuel'!$A$2:$A$10,C$1),"")</f>
         <v/>
       </c>
     </row>
@@ -3247,7 +3322,11 @@
         </is>
       </c>
       <c r="B4" s="22">
-        <f>IFERROR(AVERAGEIFS('Historique mensuel'!$C$2:$C$9,'Historique mensuel'!$B$2:$B$9,$A4,'Historique mensuel'!$A$2:$A$9,B$1),"")</f>
+        <f>IFERROR(AVERAGEIFS('Historique mensuel'!$C$2:$C$10,'Historique mensuel'!$B$2:$B$10,$A4,'Historique mensuel'!$A$2:$A$10,B$1),"")</f>
+        <v/>
+      </c>
+      <c r="C4" s="22">
+        <f>IFERROR(AVERAGEIFS('Historique mensuel'!$C$2:$C$10,'Historique mensuel'!$B$2:$B$10,$A4,'Historique mensuel'!$A$2:$A$10,C$1),"")</f>
         <v/>
       </c>
     </row>
@@ -3258,7 +3337,11 @@
         </is>
       </c>
       <c r="B5" s="22">
-        <f>IFERROR(AVERAGEIFS('Historique mensuel'!$C$2:$C$9,'Historique mensuel'!$B$2:$B$9,$A5,'Historique mensuel'!$A$2:$A$9,B$1),"")</f>
+        <f>IFERROR(AVERAGEIFS('Historique mensuel'!$C$2:$C$10,'Historique mensuel'!$B$2:$B$10,$A5,'Historique mensuel'!$A$2:$A$10,B$1),"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="22">
+        <f>IFERROR(AVERAGEIFS('Historique mensuel'!$C$2:$C$10,'Historique mensuel'!$B$2:$B$10,$A5,'Historique mensuel'!$A$2:$A$10,C$1),"")</f>
         <v/>
       </c>
     </row>
@@ -3269,7 +3352,11 @@
         </is>
       </c>
       <c r="B6" s="22">
-        <f>IFERROR(AVERAGEIFS('Historique mensuel'!$C$2:$C$9,'Historique mensuel'!$B$2:$B$9,$A6,'Historique mensuel'!$A$2:$A$9,B$1),"")</f>
+        <f>IFERROR(AVERAGEIFS('Historique mensuel'!$C$2:$C$10,'Historique mensuel'!$B$2:$B$10,$A6,'Historique mensuel'!$A$2:$A$10,B$1),"")</f>
+        <v/>
+      </c>
+      <c r="C6" s="22">
+        <f>IFERROR(AVERAGEIFS('Historique mensuel'!$C$2:$C$10,'Historique mensuel'!$B$2:$B$10,$A6,'Historique mensuel'!$A$2:$A$10,C$1),"")</f>
         <v/>
       </c>
     </row>
@@ -3280,7 +3367,11 @@
         </is>
       </c>
       <c r="B7" s="22">
-        <f>IFERROR(AVERAGEIFS('Historique mensuel'!$C$2:$C$9,'Historique mensuel'!$B$2:$B$9,$A7,'Historique mensuel'!$A$2:$A$9,B$1),"")</f>
+        <f>IFERROR(AVERAGEIFS('Historique mensuel'!$C$2:$C$10,'Historique mensuel'!$B$2:$B$10,$A7,'Historique mensuel'!$A$2:$A$10,B$1),"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="22">
+        <f>IFERROR(AVERAGEIFS('Historique mensuel'!$C$2:$C$10,'Historique mensuel'!$B$2:$B$10,$A7,'Historique mensuel'!$A$2:$A$10,C$1),"")</f>
         <v/>
       </c>
     </row>
@@ -3291,7 +3382,11 @@
         </is>
       </c>
       <c r="B8" s="22">
-        <f>IFERROR(AVERAGEIFS('Historique mensuel'!$C$2:$C$9,'Historique mensuel'!$B$2:$B$9,$A8,'Historique mensuel'!$A$2:$A$9,B$1),"")</f>
+        <f>IFERROR(AVERAGEIFS('Historique mensuel'!$C$2:$C$10,'Historique mensuel'!$B$2:$B$10,$A8,'Historique mensuel'!$A$2:$A$10,B$1),"")</f>
+        <v/>
+      </c>
+      <c r="C8" s="22">
+        <f>IFERROR(AVERAGEIFS('Historique mensuel'!$C$2:$C$10,'Historique mensuel'!$B$2:$B$10,$A8,'Historique mensuel'!$A$2:$A$10,C$1),"")</f>
         <v/>
       </c>
     </row>
@@ -3302,7 +3397,11 @@
         </is>
       </c>
       <c r="B9" s="22">
-        <f>IFERROR(AVERAGEIFS('Historique mensuel'!$C$2:$C$9,'Historique mensuel'!$B$2:$B$9,$A9,'Historique mensuel'!$A$2:$A$9,B$1),"")</f>
+        <f>IFERROR(AVERAGEIFS('Historique mensuel'!$C$2:$C$10,'Historique mensuel'!$B$2:$B$10,$A9,'Historique mensuel'!$A$2:$A$10,B$1),"")</f>
+        <v/>
+      </c>
+      <c r="C9" s="22">
+        <f>IFERROR(AVERAGEIFS('Historique mensuel'!$C$2:$C$10,'Historique mensuel'!$B$2:$B$10,$A9,'Historique mensuel'!$A$2:$A$10,C$1),"")</f>
         <v/>
       </c>
     </row>
@@ -3317,7 +3416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3423,6 +3522,16 @@
         <v>100</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="n">
+        <v>142.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3435,7 +3544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3540,41 +3649,53 @@
     </row>
     <row r="2">
       <c r="A2" s="18" t="n">
-        <v>46273</v>
+        <v>46296</v>
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>Citroën Saxo VTS 16V</t>
+          <t>Peugeot 206 RC</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>manuel</t>
+          <t>apify</t>
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E2" s="12" t="n">
-        <v>6500</v>
-      </c>
-      <c r="F2" s="12" t="n"/>
+        <v>5300</v>
+      </c>
+      <c r="F2" s="12" t="n">
+        <v>7000</v>
+      </c>
       <c r="G2" s="12" t="n">
-        <v>6600</v>
-      </c>
-      <c r="H2" s="12" t="n"/>
+        <v>9650</v>
+      </c>
+      <c r="H2" s="12" t="n">
+        <v>12125</v>
+      </c>
       <c r="I2" s="12" t="n">
-        <v>6700</v>
-      </c>
-      <c r="J2" s="15" t="n">
-        <v>153683</v>
-      </c>
-      <c r="K2" s="12" t="n"/>
-      <c r="L2" s="15" t="n"/>
-      <c r="M2" s="16" t="n"/>
-      <c r="N2" s="16" t="n"/>
+        <v>18500</v>
+      </c>
+      <c r="J2" s="15" t="n"/>
+      <c r="K2" s="12" t="n">
+        <v>9650</v>
+      </c>
+      <c r="L2" s="15" t="n">
+        <v>150000</v>
+      </c>
+      <c r="M2" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="N2" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="O2" s="17" t="n"/>
-      <c r="P2" s="16" t="n"/>
+      <c r="P2" s="16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="18" t="n">
@@ -3582,7 +3703,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Peugeot 206 RC</t>
+          <t>Citroën Saxo VTS 16V</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
@@ -3591,21 +3712,21 @@
         </is>
       </c>
       <c r="D3" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="12" t="n">
-        <v>6790</v>
+        <v>6500</v>
       </c>
       <c r="F3" s="12" t="n"/>
       <c r="G3" s="12" t="n">
-        <v>6790</v>
+        <v>6600</v>
       </c>
       <c r="H3" s="12" t="n"/>
       <c r="I3" s="12" t="n">
-        <v>6790</v>
+        <v>6700</v>
       </c>
       <c r="J3" s="15" t="n">
-        <v>244000</v>
+        <v>153683</v>
       </c>
       <c r="K3" s="12" t="n"/>
       <c r="L3" s="15" t="n"/>
@@ -3620,7 +3741,7 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>Peugeot 208 GTi 30th</t>
+          <t>Peugeot 206 RC</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -3629,21 +3750,21 @@
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>12990</v>
+        <v>6790</v>
       </c>
       <c r="F4" s="12" t="n"/>
       <c r="G4" s="12" t="n">
-        <v>15990</v>
+        <v>6790</v>
       </c>
       <c r="H4" s="12" t="n"/>
       <c r="I4" s="12" t="n">
-        <v>23490</v>
+        <v>6790</v>
       </c>
       <c r="J4" s="15" t="n">
-        <v>108000</v>
+        <v>244000</v>
       </c>
       <c r="K4" s="12" t="n"/>
       <c r="L4" s="15" t="n"/>
@@ -3658,7 +3779,7 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Porsche 911 997 Carrera S</t>
+          <t>Peugeot 208 GTi 30th</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -3667,21 +3788,21 @@
         </is>
       </c>
       <c r="D5" s="16" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>46500</v>
+        <v>12990</v>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n">
-        <v>51000</v>
+        <v>15990</v>
       </c>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n">
-        <v>74900</v>
+        <v>23490</v>
       </c>
       <c r="J5" s="15" t="n">
-        <v>100000</v>
+        <v>108000</v>
       </c>
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="15" t="n"/>
@@ -3696,7 +3817,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Porsche Boxster 986</t>
+          <t>Porsche 911 997 Carrera S</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -3705,21 +3826,21 @@
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>17986</v>
+        <v>46500</v>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n">
-        <v>22425</v>
+        <v>51000</v>
       </c>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n">
-        <v>26900</v>
+        <v>74900</v>
       </c>
       <c r="J6" s="15" t="n">
-        <v>110000</v>
+        <v>100000</v>
       </c>
       <c r="K6" s="12" t="n"/>
       <c r="L6" s="15" t="n"/>
@@ -3734,7 +3855,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Porsche Boxster 987</t>
+          <t>Porsche Boxster 986</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -3743,21 +3864,21 @@
         </is>
       </c>
       <c r="D7" s="16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>33000</v>
+        <v>17986</v>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n">
-        <v>43990</v>
+        <v>22425</v>
       </c>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n">
-        <v>72986</v>
+        <v>26900</v>
       </c>
       <c r="J7" s="15" t="n">
-        <v>65000</v>
+        <v>110000</v>
       </c>
       <c r="K7" s="12" t="n"/>
       <c r="L7" s="15" t="n"/>
@@ -3772,7 +3893,7 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Renault Clio II RS (172/182 ch)</t>
+          <t>Porsche Boxster 987</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -3781,21 +3902,21 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>6000</v>
+        <v>33000</v>
       </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n">
-        <v>8899.5</v>
+        <v>43990</v>
       </c>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n">
-        <v>11799</v>
+        <v>72986</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>168000</v>
+        <v>65000</v>
       </c>
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="15" t="n"/>
@@ -3810,7 +3931,7 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Renault Twingo 1 découvrable</t>
+          <t>Renault Clio II RS (172/182 ch)</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -3819,21 +3940,21 @@
         </is>
       </c>
       <c r="D9" s="16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>1500</v>
+        <v>6000</v>
       </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n">
-        <v>5490</v>
+        <v>8899.5</v>
       </c>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n">
-        <v>6290</v>
+        <v>11799</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>150000</v>
+        <v>168000</v>
       </c>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="15" t="n"/>
@@ -3842,8 +3963,46 @@
       <c r="O9" s="17" t="n"/>
       <c r="P9" s="16" t="n"/>
     </row>
+    <row r="10">
+      <c r="A10" s="18" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Renault Twingo 1 découvrable</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="12" t="n">
+        <v>5490</v>
+      </c>
+      <c r="H10" s="12" t="n"/>
+      <c r="I10" s="12" t="n">
+        <v>6290</v>
+      </c>
+      <c r="J10" s="15" t="n">
+        <v>150000</v>
+      </c>
+      <c r="K10" s="12" t="n"/>
+      <c r="L10" s="15" t="n"/>
+      <c r="M10" s="16" t="n"/>
+      <c r="N10" s="16" t="n"/>
+      <c r="O10" s="17" t="n"/>
+      <c r="P10" s="16" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P9"/>
+  <autoFilter ref="A1:P10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3854,7 +4013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3951,9 +4110,2250 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>206 rc</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E2" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F2" s="18" t="n"/>
+      <c r="G2" s="17">
+        <f>IF(ISNUMBER(D2),IF(ISNUMBER(F2),F2,E2)-D2,"")</f>
+        <v/>
+      </c>
+      <c r="H2" s="12" t="n">
+        <v>17900</v>
+      </c>
+      <c r="I2" s="12" t="n">
+        <v>17900</v>
+      </c>
+      <c r="J2" s="13">
+        <f>IF(AND(ISNUMBER(H2),ISNUMBER(I2),H2&gt;0),1-I2/H2,"")</f>
+        <v/>
+      </c>
+      <c r="K2" s="15" t="n"/>
+      <c r="L2" s="16" t="n"/>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>Troyes</t>
+        </is>
+      </c>
+      <c r="N2" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O2" s="10" t="inlineStr">
+        <is>
+          <t>2988747124</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>206 rc</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E3" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F3" s="18" t="n"/>
+      <c r="G3" s="17">
+        <f>IF(ISNUMBER(D3),IF(ISNUMBER(F3),F3,E3)-D3,"")</f>
+        <v/>
+      </c>
+      <c r="H3" s="12" t="n">
+        <v>11000</v>
+      </c>
+      <c r="I3" s="12" t="n">
+        <v>11000</v>
+      </c>
+      <c r="J3" s="13">
+        <f>IF(AND(ISNUMBER(H3),ISNUMBER(I3),H3&gt;0),1-I3/H3,"")</f>
+        <v/>
+      </c>
+      <c r="K3" s="15" t="n"/>
+      <c r="L3" s="16" t="n"/>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>Valserhône</t>
+        </is>
+      </c>
+      <c r="N3" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O3" s="10" t="inlineStr">
+        <is>
+          <t>3123040394</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>206 rc f2014</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E4" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F4" s="18" t="n"/>
+      <c r="G4" s="17">
+        <f>IF(ISNUMBER(D4),IF(ISNUMBER(F4),F4,E4)-D4,"")</f>
+        <v/>
+      </c>
+      <c r="H4" s="12" t="n">
+        <v>18500</v>
+      </c>
+      <c r="I4" s="12" t="n">
+        <v>18500</v>
+      </c>
+      <c r="J4" s="13">
+        <f>IF(AND(ISNUMBER(H4),ISNUMBER(I4),H4&gt;0),1-I4/H4,"")</f>
+        <v/>
+      </c>
+      <c r="K4" s="15" t="n"/>
+      <c r="L4" s="16" t="n"/>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>Blesle</t>
+        </is>
+      </c>
+      <c r="N4" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O4" s="10" t="inlineStr">
+        <is>
+          <t>3151025653</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F5" s="18" t="n"/>
+      <c r="G5" s="17">
+        <f>IF(ISNUMBER(D5),IF(ISNUMBER(F5),F5,E5)-D5,"")</f>
+        <v/>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>10500</v>
+      </c>
+      <c r="I5" s="12" t="n">
+        <v>10500</v>
+      </c>
+      <c r="J5" s="13">
+        <f>IF(AND(ISNUMBER(H5),ISNUMBER(I5),H5&gt;0),1-I5/H5,"")</f>
+        <v/>
+      </c>
+      <c r="K5" s="15" t="n"/>
+      <c r="L5" s="16" t="n"/>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>Tagnon</t>
+        </is>
+      </c>
+      <c r="N5" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O5" s="10" t="inlineStr">
+        <is>
+          <t>3193819824</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F6" s="18" t="n"/>
+      <c r="G6" s="17">
+        <f>IF(ISNUMBER(D6),IF(ISNUMBER(F6),F6,E6)-D6,"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="12" t="n">
+        <v>9500</v>
+      </c>
+      <c r="I6" s="12" t="n">
+        <v>9500</v>
+      </c>
+      <c r="J6" s="13">
+        <f>IF(AND(ISNUMBER(H6),ISNUMBER(I6),H6&gt;0),1-I6/H6,"")</f>
+        <v/>
+      </c>
+      <c r="K6" s="15" t="n"/>
+      <c r="L6" s="16" t="n"/>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>Thaon-les-Vosges</t>
+        </is>
+      </c>
+      <c r="N6" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O6" s="10" t="inlineStr">
+        <is>
+          <t>3202654340</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 rc</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F7" s="18" t="n"/>
+      <c r="G7" s="17">
+        <f>IF(ISNUMBER(D7),IF(ISNUMBER(F7),F7,E7)-D7,"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>8800</v>
+      </c>
+      <c r="I7" s="12" t="n">
+        <v>8800</v>
+      </c>
+      <c r="J7" s="13">
+        <f>IF(AND(ISNUMBER(H7),ISNUMBER(I7),H7&gt;0),1-I7/H7,"")</f>
+        <v/>
+      </c>
+      <c r="K7" s="15" t="n"/>
+      <c r="L7" s="16" t="n"/>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>Saint-Amand-Montrond</t>
+        </is>
+      </c>
+      <c r="N7" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O7" s="10" t="inlineStr">
+        <is>
+          <t>3227695185</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>PEUGEOT 206 2.0e 180 RC / LIGNE A CLAPET / COURROIE OK</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F8" s="18" t="n"/>
+      <c r="G8" s="17">
+        <f>IF(ISNUMBER(D8),IF(ISNUMBER(F8),F8,E8)-D8,"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>9990</v>
+      </c>
+      <c r="I8" s="12" t="n">
+        <v>9990</v>
+      </c>
+      <c r="J8" s="13">
+        <f>IF(AND(ISNUMBER(H8),ISNUMBER(I8),H8&gt;0),1-I8/H8,"")</f>
+        <v/>
+      </c>
+      <c r="K8" s="15" t="n"/>
+      <c r="L8" s="16" t="n"/>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="N8" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O8" s="10" t="inlineStr">
+        <is>
+          <t>3234323904</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 2.0 177ch RC - SUIVI COMPLET - DISTRIBUTION OK - BLUETOOTH</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F9" s="18" t="n"/>
+      <c r="G9" s="17">
+        <f>IF(ISNUMBER(D9),IF(ISNUMBER(F9),F9,E9)-D9,"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>13990</v>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>13990</v>
+      </c>
+      <c r="J9" s="13">
+        <f>IF(AND(ISNUMBER(H9),ISNUMBER(I9),H9&gt;0),1-I9/H9,"")</f>
+        <v/>
+      </c>
+      <c r="K9" s="15" t="n"/>
+      <c r="L9" s="16" t="n"/>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>La Ciotat</t>
+        </is>
+      </c>
+      <c r="N9" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O9" s="10" t="inlineStr">
+        <is>
+          <t>3248463615</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>206 rc</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F10" s="18" t="n"/>
+      <c r="G10" s="17">
+        <f>IF(ISNUMBER(D10),IF(ISNUMBER(F10),F10,E10)-D10,"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="12" t="n">
+        <v>6200</v>
+      </c>
+      <c r="I10" s="12" t="n">
+        <v>6200</v>
+      </c>
+      <c r="J10" s="13">
+        <f>IF(AND(ISNUMBER(H10),ISNUMBER(I10),H10&gt;0),1-I10/H10,"")</f>
+        <v/>
+      </c>
+      <c r="K10" s="15" t="n"/>
+      <c r="L10" s="16" t="n"/>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>Coulonges-sur-Sarthe</t>
+        </is>
+      </c>
+      <c r="N10" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O10" s="10" t="inlineStr">
+        <is>
+          <t>3251217335</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>206 rc</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F11" s="18" t="n"/>
+      <c r="G11" s="17">
+        <f>IF(ISNUMBER(D11),IF(ISNUMBER(F11),F11,E11)-D11,"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>11500</v>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>11500</v>
+      </c>
+      <c r="J11" s="13">
+        <f>IF(AND(ISNUMBER(H11),ISNUMBER(I11),H11&gt;0),1-I11/H11,"")</f>
+        <v/>
+      </c>
+      <c r="K11" s="15" t="n"/>
+      <c r="L11" s="16" t="n"/>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>Montaigu-Vendée</t>
+        </is>
+      </c>
+      <c r="N11" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O11" s="10" t="inlineStr">
+        <is>
+          <t>3254206684</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>206 rc</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="17">
+        <f>IF(ISNUMBER(D12),IF(ISNUMBER(F12),F12,E12)-D12,"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>7000</v>
+      </c>
+      <c r="J12" s="13">
+        <f>IF(AND(ISNUMBER(H12),ISNUMBER(I12),H12&gt;0),1-I12/H12,"")</f>
+        <v/>
+      </c>
+      <c r="K12" s="15" t="n"/>
+      <c r="L12" s="16" t="n"/>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>Sanary-sur-Mer</t>
+        </is>
+      </c>
+      <c r="N12" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O12" s="10" t="inlineStr">
+        <is>
+          <t>3256639318</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>206 rc</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F13" s="18" t="n"/>
+      <c r="G13" s="17">
+        <f>IF(ISNUMBER(D13),IF(ISNUMBER(F13),F13,E13)-D13,"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>16300</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>16300</v>
+      </c>
+      <c r="J13" s="13">
+        <f>IF(AND(ISNUMBER(H13),ISNUMBER(I13),H13&gt;0),1-I13/H13,"")</f>
+        <v/>
+      </c>
+      <c r="K13" s="15" t="n"/>
+      <c r="L13" s="16" t="n"/>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>Épernay</t>
+        </is>
+      </c>
+      <c r="N13" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O13" s="10" t="inlineStr">
+        <is>
+          <t>3258422146</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>206 rc</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="17">
+        <f>IF(ISNUMBER(D14),IF(ISNUMBER(F14),F14,E14)-D14,"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="12" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>7500</v>
+      </c>
+      <c r="J14" s="13">
+        <f>IF(AND(ISNUMBER(H14),ISNUMBER(I14),H14&gt;0),1-I14/H14,"")</f>
+        <v/>
+      </c>
+      <c r="K14" s="15" t="n"/>
+      <c r="L14" s="16" t="n"/>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>Les Grandes-Ventes</t>
+        </is>
+      </c>
+      <c r="N14" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O14" s="10" t="inlineStr">
+        <is>
+          <t>3259064609</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>206 rc 180</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="17">
+        <f>IF(ISNUMBER(D15),IF(ISNUMBER(F15),F15,E15)-D15,"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>11000</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>11000</v>
+      </c>
+      <c r="J15" s="13">
+        <f>IF(AND(ISNUMBER(H15),ISNUMBER(I15),H15&gt;0),1-I15/H15,"")</f>
+        <v/>
+      </c>
+      <c r="K15" s="15" t="n"/>
+      <c r="L15" s="16" t="n"/>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>Champagnole</t>
+        </is>
+      </c>
+      <c r="N15" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O15" s="10" t="inlineStr">
+        <is>
+          <t>3262442354</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>206 rc</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F16" s="18" t="n"/>
+      <c r="G16" s="17">
+        <f>IF(ISNUMBER(D16),IF(ISNUMBER(F16),F16,E16)-D16,"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J16" s="13">
+        <f>IF(AND(ISNUMBER(H16),ISNUMBER(I16),H16&gt;0),1-I16/H16,"")</f>
+        <v/>
+      </c>
+      <c r="K16" s="15" t="n"/>
+      <c r="L16" s="16" t="n"/>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>Figeac</t>
+        </is>
+      </c>
+      <c r="N16" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O16" s="10" t="inlineStr">
+        <is>
+          <t>3264412764</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>206 rc</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F17" s="18" t="n"/>
+      <c r="G17" s="17">
+        <f>IF(ISNUMBER(D17),IF(ISNUMBER(F17),F17,E17)-D17,"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>11000</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>11000</v>
+      </c>
+      <c r="J17" s="13">
+        <f>IF(AND(ISNUMBER(H17),ISNUMBER(I17),H17&gt;0),1-I17/H17,"")</f>
+        <v/>
+      </c>
+      <c r="K17" s="15" t="n"/>
+      <c r="L17" s="16" t="n"/>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>Caen</t>
+        </is>
+      </c>
+      <c r="N17" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O17" s="10" t="inlineStr">
+        <is>
+          <t>3265358347</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>206 RC Rouge Aden</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F18" s="18" t="n"/>
+      <c r="G18" s="17">
+        <f>IF(ISNUMBER(D18),IF(ISNUMBER(F18),F18,E18)-D18,"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>13990</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>13990</v>
+      </c>
+      <c r="J18" s="13">
+        <f>IF(AND(ISNUMBER(H18),ISNUMBER(I18),H18&gt;0),1-I18/H18,"")</f>
+        <v/>
+      </c>
+      <c r="K18" s="15" t="n"/>
+      <c r="L18" s="16" t="n"/>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>Souleuvre en Bocage</t>
+        </is>
+      </c>
+      <c r="N18" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O18" s="10" t="inlineStr">
+        <is>
+          <t>3265384769</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC - Rouge Aden - 180cv</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F19" s="18" t="n"/>
+      <c r="G19" s="17">
+        <f>IF(ISNUMBER(D19),IF(ISNUMBER(F19),F19,E19)-D19,"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>12500</v>
+      </c>
+      <c r="J19" s="13">
+        <f>IF(AND(ISNUMBER(H19),ISNUMBER(I19),H19&gt;0),1-I19/H19,"")</f>
+        <v/>
+      </c>
+      <c r="K19" s="15" t="n"/>
+      <c r="L19" s="16" t="n"/>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>Molsheim</t>
+        </is>
+      </c>
+      <c r="N19" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O19" s="10" t="inlineStr">
+        <is>
+          <t>3267576253</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 rc</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F20" s="18" t="n"/>
+      <c r="G20" s="17">
+        <f>IF(ISNUMBER(D20),IF(ISNUMBER(F20),F20,E20)-D20,"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>12700</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>12700</v>
+      </c>
+      <c r="J20" s="13">
+        <f>IF(AND(ISNUMBER(H20),ISNUMBER(I20),H20&gt;0),1-I20/H20,"")</f>
+        <v/>
+      </c>
+      <c r="K20" s="15" t="n"/>
+      <c r="L20" s="16" t="n"/>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>Lantenne-Vertière</t>
+        </is>
+      </c>
+      <c r="N20" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O20" s="10" t="inlineStr">
+        <is>
+          <t>3268704461</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC 2.0 177ch</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="17">
+        <f>IF(ISNUMBER(D21),IF(ISNUMBER(F21),F21,E21)-D21,"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>9800</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>9800</v>
+      </c>
+      <c r="J21" s="13">
+        <f>IF(AND(ISNUMBER(H21),ISNUMBER(I21),H21&gt;0),1-I21/H21,"")</f>
+        <v/>
+      </c>
+      <c r="K21" s="15" t="n"/>
+      <c r="L21" s="16" t="n"/>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>Châteaudun</t>
+        </is>
+      </c>
+      <c r="N21" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O21" s="10" t="inlineStr">
+        <is>
+          <t>3269057716</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>206 rc</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E22" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F22" s="18" t="n"/>
+      <c r="G22" s="17">
+        <f>IF(ISNUMBER(D22),IF(ISNUMBER(F22),F22,E22)-D22,"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>11500</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>11500</v>
+      </c>
+      <c r="J22" s="13">
+        <f>IF(AND(ISNUMBER(H22),ISNUMBER(I22),H22&gt;0),1-I22/H22,"")</f>
+        <v/>
+      </c>
+      <c r="K22" s="15" t="n"/>
+      <c r="L22" s="16" t="n"/>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>Béziers</t>
+        </is>
+      </c>
+      <c r="N22" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O22" s="10" t="inlineStr">
+        <is>
+          <t>3270523427</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 rc 2.0 180</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F23" s="18" t="n"/>
+      <c r="G23" s="17">
+        <f>IF(ISNUMBER(D23),IF(ISNUMBER(F23),F23,E23)-D23,"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>13990</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>13990</v>
+      </c>
+      <c r="J23" s="13">
+        <f>IF(AND(ISNUMBER(H23),ISNUMBER(I23),H23&gt;0),1-I23/H23,"")</f>
+        <v/>
+      </c>
+      <c r="K23" s="15" t="n"/>
+      <c r="L23" s="16" t="n"/>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>Saint-Féliu-d'Avall</t>
+        </is>
+      </c>
+      <c r="N23" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O23" s="10" t="inlineStr">
+        <is>
+          <t>3270650631</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 rc</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F24" s="18" t="n"/>
+      <c r="G24" s="17">
+        <f>IF(ISNUMBER(D24),IF(ISNUMBER(F24),F24,E24)-D24,"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="12" t="n">
+        <v>7800</v>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>7800</v>
+      </c>
+      <c r="J24" s="13">
+        <f>IF(AND(ISNUMBER(H24),ISNUMBER(I24),H24&gt;0),1-I24/H24,"")</f>
+        <v/>
+      </c>
+      <c r="K24" s="15" t="n"/>
+      <c r="L24" s="16" t="n"/>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>Lavelanet</t>
+        </is>
+      </c>
+      <c r="N24" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O24" s="10" t="inlineStr">
+        <is>
+          <t>3271026847</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>206 rc</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F25" s="18" t="n"/>
+      <c r="G25" s="17">
+        <f>IF(ISNUMBER(D25),IF(ISNUMBER(F25),F25,E25)-D25,"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>7000</v>
+      </c>
+      <c r="J25" s="13">
+        <f>IF(AND(ISNUMBER(H25),ISNUMBER(I25),H25&gt;0),1-I25/H25,"")</f>
+        <v/>
+      </c>
+      <c r="K25" s="15" t="n"/>
+      <c r="L25" s="16" t="n"/>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="N25" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O25" s="10" t="inlineStr">
+        <is>
+          <t>3271661241</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>206 rc</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F26" s="18" t="n"/>
+      <c r="G26" s="17">
+        <f>IF(ISNUMBER(D26),IF(ISNUMBER(F26),F26,E26)-D26,"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="12" t="n">
+        <v>5900</v>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>5900</v>
+      </c>
+      <c r="J26" s="13">
+        <f>IF(AND(ISNUMBER(H26),ISNUMBER(I26),H26&gt;0),1-I26/H26,"")</f>
+        <v/>
+      </c>
+      <c r="K26" s="15" t="n"/>
+      <c r="L26" s="16" t="n"/>
+      <c r="M26" s="10" t="inlineStr">
+        <is>
+          <t>Tulle</t>
+        </is>
+      </c>
+      <c r="N26" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O26" s="10" t="inlineStr">
+        <is>
+          <t>3273170431</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 Rc</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F27" s="18" t="n"/>
+      <c r="G27" s="17">
+        <f>IF(ISNUMBER(D27),IF(ISNUMBER(F27),F27,E27)-D27,"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="12" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J27" s="13">
+        <f>IF(AND(ISNUMBER(H27),ISNUMBER(I27),H27&gt;0),1-I27/H27,"")</f>
+        <v/>
+      </c>
+      <c r="K27" s="15" t="n"/>
+      <c r="L27" s="16" t="n"/>
+      <c r="M27" s="10" t="inlineStr">
+        <is>
+          <t>Saint-Cyr-les-Vignes</t>
+        </is>
+      </c>
+      <c r="N27" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O27" s="10" t="inlineStr">
+        <is>
+          <t>3275009272</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>206 rc</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F28" s="18" t="n"/>
+      <c r="G28" s="17">
+        <f>IF(ISNUMBER(D28),IF(ISNUMBER(F28),F28,E28)-D28,"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>7500</v>
+      </c>
+      <c r="J28" s="13">
+        <f>IF(AND(ISNUMBER(H28),ISNUMBER(I28),H28&gt;0),1-I28/H28,"")</f>
+        <v/>
+      </c>
+      <c r="K28" s="15" t="n"/>
+      <c r="L28" s="16" t="n"/>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>Perriers-sur-Andelle</t>
+        </is>
+      </c>
+      <c r="N28" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O28" s="10" t="inlineStr">
+        <is>
+          <t>3275531733</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>206 rc</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F29" s="18" t="n"/>
+      <c r="G29" s="17">
+        <f>IF(ISNUMBER(D29),IF(ISNUMBER(F29),F29,E29)-D29,"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>13499</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>13499</v>
+      </c>
+      <c r="J29" s="13">
+        <f>IF(AND(ISNUMBER(H29),ISNUMBER(I29),H29&gt;0),1-I29/H29,"")</f>
+        <v/>
+      </c>
+      <c r="K29" s="15" t="n"/>
+      <c r="L29" s="16" t="n"/>
+      <c r="M29" s="10" t="inlineStr">
+        <is>
+          <t>Saint-Hilaire-Saint-Mesmin</t>
+        </is>
+      </c>
+      <c r="N29" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O29" s="10" t="inlineStr">
+        <is>
+          <t>3276061576</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>206 rc line 1.6 110 cv</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F30" s="18" t="n"/>
+      <c r="G30" s="17">
+        <f>IF(ISNUMBER(D30),IF(ISNUMBER(F30),F30,E30)-D30,"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>6800</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>6800</v>
+      </c>
+      <c r="J30" s="13">
+        <f>IF(AND(ISNUMBER(H30),ISNUMBER(I30),H30&gt;0),1-I30/H30,"")</f>
+        <v/>
+      </c>
+      <c r="K30" s="15" t="n"/>
+      <c r="L30" s="16" t="n"/>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>Cernay</t>
+        </is>
+      </c>
+      <c r="N30" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O30" s="10" t="inlineStr">
+        <is>
+          <t>3276929411</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC 2.0 177ch - Bleu Récif</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F31" s="18" t="n"/>
+      <c r="G31" s="17">
+        <f>IF(ISNUMBER(D31),IF(ISNUMBER(F31),F31,E31)-D31,"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>5300</v>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>5300</v>
+      </c>
+      <c r="J31" s="13">
+        <f>IF(AND(ISNUMBER(H31),ISNUMBER(I31),H31&gt;0),1-I31/H31,"")</f>
+        <v/>
+      </c>
+      <c r="K31" s="15" t="n"/>
+      <c r="L31" s="16" t="n"/>
+      <c r="M31" s="10" t="inlineStr">
+        <is>
+          <t>Belley</t>
+        </is>
+      </c>
+      <c r="N31" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O31" s="10" t="inlineStr">
+        <is>
+          <t>3277073683</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 rc</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F32" s="18" t="n"/>
+      <c r="G32" s="17">
+        <f>IF(ISNUMBER(D32),IF(ISNUMBER(F32),F32,E32)-D32,"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>11000</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>11000</v>
+      </c>
+      <c r="J32" s="13">
+        <f>IF(AND(ISNUMBER(H32),ISNUMBER(I32),H32&gt;0),1-I32/H32,"")</f>
+        <v/>
+      </c>
+      <c r="K32" s="15" t="n"/>
+      <c r="L32" s="16" t="n"/>
+      <c r="M32" s="10" t="inlineStr">
+        <is>
+          <t>Saint-Cyr-de-Favières</t>
+        </is>
+      </c>
+      <c r="N32" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O32" s="10" t="inlineStr">
+        <is>
+          <t>3277840482</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>206 rc</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F33" s="18" t="n"/>
+      <c r="G33" s="17">
+        <f>IF(ISNUMBER(D33),IF(ISNUMBER(F33),F33,E33)-D33,"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="12" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I33" s="12" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J33" s="13">
+        <f>IF(AND(ISNUMBER(H33),ISNUMBER(I33),H33&gt;0),1-I33/H33,"")</f>
+        <v/>
+      </c>
+      <c r="K33" s="15" t="n"/>
+      <c r="L33" s="16" t="n"/>
+      <c r="M33" s="10" t="inlineStr">
+        <is>
+          <t>La Côte-Saint-André</t>
+        </is>
+      </c>
+      <c r="N33" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O33" s="10" t="inlineStr">
+        <is>
+          <t>3278317897</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>206 rc</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E34" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F34" s="18" t="n"/>
+      <c r="G34" s="17">
+        <f>IF(ISNUMBER(D34),IF(ISNUMBER(F34),F34,E34)-D34,"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>8500</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>8500</v>
+      </c>
+      <c r="J34" s="13">
+        <f>IF(AND(ISNUMBER(H34),ISNUMBER(I34),H34&gt;0),1-I34/H34,"")</f>
+        <v/>
+      </c>
+      <c r="K34" s="15" t="n"/>
+      <c r="L34" s="16" t="n"/>
+      <c r="M34" s="10" t="inlineStr">
+        <is>
+          <t>Perrecy-les-Forges</t>
+        </is>
+      </c>
+      <c r="N34" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O34" s="10" t="inlineStr">
+        <is>
+          <t>3278631826</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D35" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F35" s="18" t="n"/>
+      <c r="G35" s="17">
+        <f>IF(ISNUMBER(D35),IF(ISNUMBER(F35),F35,E35)-D35,"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="12" t="n">
+        <v>5400</v>
+      </c>
+      <c r="I35" s="12" t="n">
+        <v>5400</v>
+      </c>
+      <c r="J35" s="13">
+        <f>IF(AND(ISNUMBER(H35),ISNUMBER(I35),H35&gt;0),1-I35/H35,"")</f>
+        <v/>
+      </c>
+      <c r="K35" s="15" t="n"/>
+      <c r="L35" s="16" t="n"/>
+      <c r="M35" s="10" t="inlineStr">
+        <is>
+          <t>La Roche-sur-Foron</t>
+        </is>
+      </c>
+      <c r="N35" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O35" s="10" t="inlineStr">
+        <is>
+          <t>3278866640</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F36" s="18" t="n"/>
+      <c r="G36" s="17">
+        <f>IF(ISNUMBER(D36),IF(ISNUMBER(F36),F36,E36)-D36,"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="12" t="n">
+        <v>14500</v>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>14500</v>
+      </c>
+      <c r="J36" s="13">
+        <f>IF(AND(ISNUMBER(H36),ISNUMBER(I36),H36&gt;0),1-I36/H36,"")</f>
+        <v/>
+      </c>
+      <c r="K36" s="15" t="n"/>
+      <c r="L36" s="16" t="n"/>
+      <c r="M36" s="10" t="inlineStr">
+        <is>
+          <t>Chamalières</t>
+        </is>
+      </c>
+      <c r="N36" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O36" s="10" t="inlineStr">
+        <is>
+          <t>3278894245</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>206 rc</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D37" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E37" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F37" s="18" t="n"/>
+      <c r="G37" s="17">
+        <f>IF(ISNUMBER(D37),IF(ISNUMBER(F37),F37,E37)-D37,"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="12" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I37" s="12" t="n">
+        <v>9000</v>
+      </c>
+      <c r="J37" s="13">
+        <f>IF(AND(ISNUMBER(H37),ISNUMBER(I37),H37&gt;0),1-I37/H37,"")</f>
+        <v/>
+      </c>
+      <c r="K37" s="15" t="n"/>
+      <c r="L37" s="16" t="n"/>
+      <c r="M37" s="10" t="inlineStr">
+        <is>
+          <t>La Clayette</t>
+        </is>
+      </c>
+      <c r="N37" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O37" s="10" t="inlineStr">
+        <is>
+          <t>3279039279</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>206 rc</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D38" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E38" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F38" s="18" t="n"/>
+      <c r="G38" s="17">
+        <f>IF(ISNUMBER(D38),IF(ISNUMBER(F38),F38,E38)-D38,"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="12" t="n">
+        <v>5900</v>
+      </c>
+      <c r="I38" s="12" t="n">
+        <v>5900</v>
+      </c>
+      <c r="J38" s="13">
+        <f>IF(AND(ISNUMBER(H38),ISNUMBER(I38),H38&gt;0),1-I38/H38,"")</f>
+        <v/>
+      </c>
+      <c r="K38" s="15" t="n"/>
+      <c r="L38" s="16" t="n"/>
+      <c r="M38" s="10" t="inlineStr">
+        <is>
+          <t>Lons-le-Saunier</t>
+        </is>
+      </c>
+      <c r="N38" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O38" s="10" t="inlineStr">
+        <is>
+          <t>3279053465</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 rc</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D39" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F39" s="18" t="n"/>
+      <c r="G39" s="17">
+        <f>IF(ISNUMBER(D39),IF(ISNUMBER(F39),F39,E39)-D39,"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>9190</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>9190</v>
+      </c>
+      <c r="J39" s="13">
+        <f>IF(AND(ISNUMBER(H39),ISNUMBER(I39),H39&gt;0),1-I39/H39,"")</f>
+        <v/>
+      </c>
+      <c r="K39" s="15" t="n"/>
+      <c r="L39" s="16" t="n"/>
+      <c r="M39" s="10" t="inlineStr">
+        <is>
+          <t>Saint-Dizier</t>
+        </is>
+      </c>
+      <c r="N39" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O39" s="10" t="inlineStr">
+        <is>
+          <t>3279236263</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E40" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F40" s="18" t="n"/>
+      <c r="G40" s="17">
+        <f>IF(ISNUMBER(D40),IF(ISNUMBER(F40),F40,E40)-D40,"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="12" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I40" s="12" t="n">
+        <v>6500</v>
+      </c>
+      <c r="J40" s="13">
+        <f>IF(AND(ISNUMBER(H40),ISNUMBER(I40),H40&gt;0),1-I40/H40,"")</f>
+        <v/>
+      </c>
+      <c r="K40" s="15" t="n"/>
+      <c r="L40" s="16" t="n"/>
+      <c r="M40" s="10" t="inlineStr">
+        <is>
+          <t>Pirmil</t>
+        </is>
+      </c>
+      <c r="N40" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O40" s="10" t="inlineStr">
+        <is>
+          <t>3279820686</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 rc 20.16v</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>En vente</t>
+        </is>
+      </c>
+      <c r="D41" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F41" s="18" t="n"/>
+      <c r="G41" s="17">
+        <f>IF(ISNUMBER(D41),IF(ISNUMBER(F41),F41,E41)-D41,"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J41" s="13">
+        <f>IF(AND(ISNUMBER(H41),ISNUMBER(I41),H41&gt;0),1-I41/H41,"")</f>
+        <v/>
+      </c>
+      <c r="K41" s="15" t="n"/>
+      <c r="L41" s="16" t="n"/>
+      <c r="M41" s="10" t="inlineStr">
+        <is>
+          <t>Erstein</t>
+        </is>
+      </c>
+      <c r="N41" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="O41" s="10" t="inlineStr">
+        <is>
+          <t>3280095370</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O2"/>
+  <autoFilter ref="A1:O41"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3964,7 +6364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4031,16 +6431,200 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC 2.0 177ch - Bleu Récif</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="n">
+        <v>5300</v>
+      </c>
+      <c r="D2" s="12" t="n">
+        <v>9650</v>
+      </c>
+      <c r="E2" s="13">
+        <f>IF(AND(ISNUMBER(C2),ISNUMBER(D2),D2&gt;0),1-C2/D2,"")</f>
+        <v/>
+      </c>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="16" t="n"/>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>Belley</t>
+        </is>
+      </c>
+      <c r="I2" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="J2" s="18" t="n">
+        <v>46296</v>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Aucune annonce nettement sous la cote au dernier relevé.</t>
-        </is>
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="n">
+        <v>5400</v>
+      </c>
+      <c r="D3" s="12" t="n">
+        <v>9650</v>
+      </c>
+      <c r="E3" s="13">
+        <f>IF(AND(ISNUMBER(C3),ISNUMBER(D3),D3&gt;0),1-C3/D3,"")</f>
+        <v/>
+      </c>
+      <c r="F3" s="15" t="n"/>
+      <c r="G3" s="16" t="n"/>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>La Roche-sur-Foron</t>
+        </is>
+      </c>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="J3" s="18" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>206 rc</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="n">
+        <v>5900</v>
+      </c>
+      <c r="D4" s="12" t="n">
+        <v>9650</v>
+      </c>
+      <c r="E4" s="13">
+        <f>IF(AND(ISNUMBER(C4),ISNUMBER(D4),D4&gt;0),1-C4/D4,"")</f>
+        <v/>
+      </c>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="16" t="n"/>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>Tulle</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="J4" s="18" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>206 rc</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>5900</v>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>9650</v>
+      </c>
+      <c r="E5" s="13">
+        <f>IF(AND(ISNUMBER(C5),ISNUMBER(D5),D5&gt;0),1-C5/D5,"")</f>
+        <v/>
+      </c>
+      <c r="F5" s="15" t="n"/>
+      <c r="G5" s="16" t="n"/>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>Lons-le-Saunier</t>
+        </is>
+      </c>
+      <c r="I5" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Peugeot 206 RC</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>206 rc</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>9650</v>
+      </c>
+      <c r="E6" s="13">
+        <f>IF(AND(ISNUMBER(C6),ISNUMBER(D6),D6&gt;0),1-C6/D6,"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>La Côte-Saint-André</t>
+        </is>
+      </c>
+      <c r="I6" s="19" t="inlineStr">
+        <is>
+          <t>Voir</t>
+        </is>
+      </c>
+      <c r="J6" s="18" t="n">
+        <v>46296</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J2"/>
+  <autoFilter ref="A1:J6"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/cote-auto.xlsx
+++ b/cote-auto.xlsx
@@ -1542,12 +1542,12 @@
         <v/>
       </c>
       <c r="I9" s="14" t="n">
-        <v>0.421</v>
+        <v>0.611</v>
       </c>
       <c r="J9" s="14" t="n"/>
       <c r="K9" s="14" t="n"/>
       <c r="L9" s="12" t="n">
-        <v>9650</v>
+        <v>10940</v>
       </c>
       <c r="M9" s="15" t="n">
         <v>150000</v>
@@ -2914,7 +2914,7 @@
         <v>12125</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>9650</v>
+        <v>10940</v>
       </c>
       <c r="H4" s="14">
         <f>IF(AND($B4=$B3,ISNUMBER(G4),ISNUMBER(G3)),G4/G3-1,"")</f>
@@ -2924,7 +2924,7 @@
         <v>40</v>
       </c>
       <c r="J4" s="16" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K4" s="16" t="n">
         <v>0</v>
@@ -3679,15 +3679,17 @@
       <c r="I2" s="12" t="n">
         <v>18500</v>
       </c>
-      <c r="J2" s="15" t="n"/>
+      <c r="J2" s="15" t="n">
+        <v>162000</v>
+      </c>
       <c r="K2" s="12" t="n">
-        <v>9650</v>
+        <v>10940</v>
       </c>
       <c r="L2" s="15" t="n">
         <v>150000</v>
       </c>
       <c r="M2" s="16" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N2" s="16" t="n">
         <v>0</v>
@@ -4147,7 +4149,9 @@
         <f>IF(AND(ISNUMBER(H2),ISNUMBER(I2),H2&gt;0),1-I2/H2,"")</f>
         <v/>
       </c>
-      <c r="K2" s="15" t="n"/>
+      <c r="K2" s="15" t="n">
+        <v>74000</v>
+      </c>
       <c r="L2" s="16" t="n"/>
       <c r="M2" s="10" t="inlineStr">
         <is>
@@ -4202,7 +4206,9 @@
         <f>IF(AND(ISNUMBER(H3),ISNUMBER(I3),H3&gt;0),1-I3/H3,"")</f>
         <v/>
       </c>
-      <c r="K3" s="15" t="n"/>
+      <c r="K3" s="15" t="n">
+        <v>138000</v>
+      </c>
       <c r="L3" s="16" t="n"/>
       <c r="M3" s="10" t="inlineStr">
         <is>
@@ -4257,7 +4263,9 @@
         <f>IF(AND(ISNUMBER(H4),ISNUMBER(I4),H4&gt;0),1-I4/H4,"")</f>
         <v/>
       </c>
-      <c r="K4" s="15" t="n"/>
+      <c r="K4" s="15" t="n">
+        <v>240000</v>
+      </c>
       <c r="L4" s="16" t="n"/>
       <c r="M4" s="10" t="inlineStr">
         <is>
@@ -4312,7 +4320,9 @@
         <f>IF(AND(ISNUMBER(H5),ISNUMBER(I5),H5&gt;0),1-I5/H5,"")</f>
         <v/>
       </c>
-      <c r="K5" s="15" t="n"/>
+      <c r="K5" s="15" t="n">
+        <v>114000</v>
+      </c>
       <c r="L5" s="16" t="n"/>
       <c r="M5" s="10" t="inlineStr">
         <is>
@@ -4367,7 +4377,9 @@
         <f>IF(AND(ISNUMBER(H6),ISNUMBER(I6),H6&gt;0),1-I6/H6,"")</f>
         <v/>
       </c>
-      <c r="K6" s="15" t="n"/>
+      <c r="K6" s="15" t="n">
+        <v>152000</v>
+      </c>
       <c r="L6" s="16" t="n"/>
       <c r="M6" s="10" t="inlineStr">
         <is>
@@ -4422,7 +4434,9 @@
         <f>IF(AND(ISNUMBER(H7),ISNUMBER(I7),H7&gt;0),1-I7/H7,"")</f>
         <v/>
       </c>
-      <c r="K7" s="15" t="n"/>
+      <c r="K7" s="15" t="n">
+        <v>197500</v>
+      </c>
       <c r="L7" s="16" t="n"/>
       <c r="M7" s="10" t="inlineStr">
         <is>
@@ -4477,7 +4491,9 @@
         <f>IF(AND(ISNUMBER(H8),ISNUMBER(I8),H8&gt;0),1-I8/H8,"")</f>
         <v/>
       </c>
-      <c r="K8" s="15" t="n"/>
+      <c r="K8" s="15" t="n">
+        <v>150000</v>
+      </c>
       <c r="L8" s="16" t="n"/>
       <c r="M8" s="10" t="inlineStr">
         <is>
@@ -4532,7 +4548,9 @@
         <f>IF(AND(ISNUMBER(H9),ISNUMBER(I9),H9&gt;0),1-I9/H9,"")</f>
         <v/>
       </c>
-      <c r="K9" s="15" t="n"/>
+      <c r="K9" s="15" t="n">
+        <v>67500</v>
+      </c>
       <c r="L9" s="16" t="n"/>
       <c r="M9" s="10" t="inlineStr">
         <is>
@@ -4587,7 +4605,9 @@
         <f>IF(AND(ISNUMBER(H10),ISNUMBER(I10),H10&gt;0),1-I10/H10,"")</f>
         <v/>
       </c>
-      <c r="K10" s="15" t="n"/>
+      <c r="K10" s="15" t="n">
+        <v>215500</v>
+      </c>
       <c r="L10" s="16" t="n"/>
       <c r="M10" s="10" t="inlineStr">
         <is>
@@ -4642,7 +4662,9 @@
         <f>IF(AND(ISNUMBER(H11),ISNUMBER(I11),H11&gt;0),1-I11/H11,"")</f>
         <v/>
       </c>
-      <c r="K11" s="15" t="n"/>
+      <c r="K11" s="15" t="n">
+        <v>118200</v>
+      </c>
       <c r="L11" s="16" t="n"/>
       <c r="M11" s="10" t="inlineStr">
         <is>
@@ -4697,7 +4719,9 @@
         <f>IF(AND(ISNUMBER(H12),ISNUMBER(I12),H12&gt;0),1-I12/H12,"")</f>
         <v/>
       </c>
-      <c r="K12" s="15" t="n"/>
+      <c r="K12" s="15" t="n">
+        <v>215000</v>
+      </c>
       <c r="L12" s="16" t="n"/>
       <c r="M12" s="10" t="inlineStr">
         <is>
@@ -4752,7 +4776,9 @@
         <f>IF(AND(ISNUMBER(H13),ISNUMBER(I13),H13&gt;0),1-I13/H13,"")</f>
         <v/>
       </c>
-      <c r="K13" s="15" t="n"/>
+      <c r="K13" s="15" t="n">
+        <v>60600</v>
+      </c>
       <c r="L13" s="16" t="n"/>
       <c r="M13" s="10" t="inlineStr">
         <is>
@@ -4807,7 +4833,9 @@
         <f>IF(AND(ISNUMBER(H14),ISNUMBER(I14),H14&gt;0),1-I14/H14,"")</f>
         <v/>
       </c>
-      <c r="K14" s="15" t="n"/>
+      <c r="K14" s="15" t="n">
+        <v>220000</v>
+      </c>
       <c r="L14" s="16" t="n"/>
       <c r="M14" s="10" t="inlineStr">
         <is>
@@ -4862,7 +4890,9 @@
         <f>IF(AND(ISNUMBER(H15),ISNUMBER(I15),H15&gt;0),1-I15/H15,"")</f>
         <v/>
       </c>
-      <c r="K15" s="15" t="n"/>
+      <c r="K15" s="15" t="n">
+        <v>154500</v>
+      </c>
       <c r="L15" s="16" t="n"/>
       <c r="M15" s="10" t="inlineStr">
         <is>
@@ -4917,7 +4947,9 @@
         <f>IF(AND(ISNUMBER(H16),ISNUMBER(I16),H16&gt;0),1-I16/H16,"")</f>
         <v/>
       </c>
-      <c r="K16" s="15" t="n"/>
+      <c r="K16" s="15" t="n">
+        <v>123000</v>
+      </c>
       <c r="L16" s="16" t="n"/>
       <c r="M16" s="10" t="inlineStr">
         <is>
@@ -4972,7 +5004,9 @@
         <f>IF(AND(ISNUMBER(H17),ISNUMBER(I17),H17&gt;0),1-I17/H17,"")</f>
         <v/>
       </c>
-      <c r="K17" s="15" t="n"/>
+      <c r="K17" s="15" t="n">
+        <v>147000</v>
+      </c>
       <c r="L17" s="16" t="n"/>
       <c r="M17" s="10" t="inlineStr">
         <is>
@@ -5027,7 +5061,9 @@
         <f>IF(AND(ISNUMBER(H18),ISNUMBER(I18),H18&gt;0),1-I18/H18,"")</f>
         <v/>
       </c>
-      <c r="K18" s="15" t="n"/>
+      <c r="K18" s="15" t="n">
+        <v>98842</v>
+      </c>
       <c r="L18" s="16" t="n"/>
       <c r="M18" s="10" t="inlineStr">
         <is>
@@ -5082,7 +5118,9 @@
         <f>IF(AND(ISNUMBER(H19),ISNUMBER(I19),H19&gt;0),1-I19/H19,"")</f>
         <v/>
       </c>
-      <c r="K19" s="15" t="n"/>
+      <c r="K19" s="15" t="n">
+        <v>131500</v>
+      </c>
       <c r="L19" s="16" t="n"/>
       <c r="M19" s="10" t="inlineStr">
         <is>
@@ -5137,7 +5175,9 @@
         <f>IF(AND(ISNUMBER(H20),ISNUMBER(I20),H20&gt;0),1-I20/H20,"")</f>
         <v/>
       </c>
-      <c r="K20" s="15" t="n"/>
+      <c r="K20" s="15" t="n">
+        <v>123000</v>
+      </c>
       <c r="L20" s="16" t="n"/>
       <c r="M20" s="10" t="inlineStr">
         <is>
@@ -5192,7 +5232,9 @@
         <f>IF(AND(ISNUMBER(H21),ISNUMBER(I21),H21&gt;0),1-I21/H21,"")</f>
         <v/>
       </c>
-      <c r="K21" s="15" t="n"/>
+      <c r="K21" s="15" t="n">
+        <v>165500</v>
+      </c>
       <c r="L21" s="16" t="n"/>
       <c r="M21" s="10" t="inlineStr">
         <is>
@@ -5247,7 +5289,9 @@
         <f>IF(AND(ISNUMBER(H22),ISNUMBER(I22),H22&gt;0),1-I22/H22,"")</f>
         <v/>
       </c>
-      <c r="K22" s="15" t="n"/>
+      <c r="K22" s="15" t="n">
+        <v>120000</v>
+      </c>
       <c r="L22" s="16" t="n"/>
       <c r="M22" s="10" t="inlineStr">
         <is>
@@ -5302,7 +5346,9 @@
         <f>IF(AND(ISNUMBER(H23),ISNUMBER(I23),H23&gt;0),1-I23/H23,"")</f>
         <v/>
       </c>
-      <c r="K23" s="15" t="n"/>
+      <c r="K23" s="15" t="n">
+        <v>125800</v>
+      </c>
       <c r="L23" s="16" t="n"/>
       <c r="M23" s="10" t="inlineStr">
         <is>
@@ -5357,7 +5403,9 @@
         <f>IF(AND(ISNUMBER(H24),ISNUMBER(I24),H24&gt;0),1-I24/H24,"")</f>
         <v/>
       </c>
-      <c r="K24" s="15" t="n"/>
+      <c r="K24" s="15" t="n">
+        <v>197000</v>
+      </c>
       <c r="L24" s="16" t="n"/>
       <c r="M24" s="10" t="inlineStr">
         <is>
@@ -5412,7 +5460,9 @@
         <f>IF(AND(ISNUMBER(H25),ISNUMBER(I25),H25&gt;0),1-I25/H25,"")</f>
         <v/>
       </c>
-      <c r="K25" s="15" t="n"/>
+      <c r="K25" s="15" t="n">
+        <v>254000</v>
+      </c>
       <c r="L25" s="16" t="n"/>
       <c r="M25" s="10" t="inlineStr">
         <is>
@@ -5467,7 +5517,9 @@
         <f>IF(AND(ISNUMBER(H26),ISNUMBER(I26),H26&gt;0),1-I26/H26,"")</f>
         <v/>
       </c>
-      <c r="K26" s="15" t="n"/>
+      <c r="K26" s="15" t="n">
+        <v>159000</v>
+      </c>
       <c r="L26" s="16" t="n"/>
       <c r="M26" s="10" t="inlineStr">
         <is>
@@ -5522,7 +5574,9 @@
         <f>IF(AND(ISNUMBER(H27),ISNUMBER(I27),H27&gt;0),1-I27/H27,"")</f>
         <v/>
       </c>
-      <c r="K27" s="15" t="n"/>
+      <c r="K27" s="15" t="n">
+        <v>222000</v>
+      </c>
       <c r="L27" s="16" t="n"/>
       <c r="M27" s="10" t="inlineStr">
         <is>
@@ -5577,7 +5631,9 @@
         <f>IF(AND(ISNUMBER(H28),ISNUMBER(I28),H28&gt;0),1-I28/H28,"")</f>
         <v/>
       </c>
-      <c r="K28" s="15" t="n"/>
+      <c r="K28" s="15" t="n">
+        <v>290000</v>
+      </c>
       <c r="L28" s="16" t="n"/>
       <c r="M28" s="10" t="inlineStr">
         <is>
@@ -5632,7 +5688,9 @@
         <f>IF(AND(ISNUMBER(H29),ISNUMBER(I29),H29&gt;0),1-I29/H29,"")</f>
         <v/>
       </c>
-      <c r="K29" s="15" t="n"/>
+      <c r="K29" s="15" t="n">
+        <v>128000</v>
+      </c>
       <c r="L29" s="16" t="n"/>
       <c r="M29" s="10" t="inlineStr">
         <is>
@@ -5687,7 +5745,9 @@
         <f>IF(AND(ISNUMBER(H30),ISNUMBER(I30),H30&gt;0),1-I30/H30,"")</f>
         <v/>
       </c>
-      <c r="K30" s="15" t="n"/>
+      <c r="K30" s="15" t="n">
+        <v>124000</v>
+      </c>
       <c r="L30" s="16" t="n"/>
       <c r="M30" s="10" t="inlineStr">
         <is>
@@ -5742,7 +5802,9 @@
         <f>IF(AND(ISNUMBER(H31),ISNUMBER(I31),H31&gt;0),1-I31/H31,"")</f>
         <v/>
       </c>
-      <c r="K31" s="15" t="n"/>
+      <c r="K31" s="15" t="n">
+        <v>234000</v>
+      </c>
       <c r="L31" s="16" t="n"/>
       <c r="M31" s="10" t="inlineStr">
         <is>
@@ -5797,7 +5859,9 @@
         <f>IF(AND(ISNUMBER(H32),ISNUMBER(I32),H32&gt;0),1-I32/H32,"")</f>
         <v/>
       </c>
-      <c r="K32" s="15" t="n"/>
+      <c r="K32" s="15" t="n">
+        <v>182000</v>
+      </c>
       <c r="L32" s="16" t="n"/>
       <c r="M32" s="10" t="inlineStr">
         <is>
@@ -5852,7 +5916,9 @@
         <f>IF(AND(ISNUMBER(H33),ISNUMBER(I33),H33&gt;0),1-I33/H33,"")</f>
         <v/>
       </c>
-      <c r="K33" s="15" t="n"/>
+      <c r="K33" s="15" t="n">
+        <v>291000</v>
+      </c>
       <c r="L33" s="16" t="n"/>
       <c r="M33" s="10" t="inlineStr">
         <is>
@@ -5907,7 +5973,9 @@
         <f>IF(AND(ISNUMBER(H34),ISNUMBER(I34),H34&gt;0),1-I34/H34,"")</f>
         <v/>
       </c>
-      <c r="K34" s="15" t="n"/>
+      <c r="K34" s="15" t="n">
+        <v>192000</v>
+      </c>
       <c r="L34" s="16" t="n"/>
       <c r="M34" s="10" t="inlineStr">
         <is>
@@ -5962,7 +6030,9 @@
         <f>IF(AND(ISNUMBER(H35),ISNUMBER(I35),H35&gt;0),1-I35/H35,"")</f>
         <v/>
       </c>
-      <c r="K35" s="15" t="n"/>
+      <c r="K35" s="15" t="n">
+        <v>244000</v>
+      </c>
       <c r="L35" s="16" t="n"/>
       <c r="M35" s="10" t="inlineStr">
         <is>
@@ -6017,7 +6087,9 @@
         <f>IF(AND(ISNUMBER(H36),ISNUMBER(I36),H36&gt;0),1-I36/H36,"")</f>
         <v/>
       </c>
-      <c r="K36" s="15" t="n"/>
+      <c r="K36" s="15" t="n">
+        <v>111000</v>
+      </c>
       <c r="L36" s="16" t="n"/>
       <c r="M36" s="10" t="inlineStr">
         <is>
@@ -6072,7 +6144,9 @@
         <f>IF(AND(ISNUMBER(H37),ISNUMBER(I37),H37&gt;0),1-I37/H37,"")</f>
         <v/>
       </c>
-      <c r="K37" s="15" t="n"/>
+      <c r="K37" s="15" t="n">
+        <v>203368</v>
+      </c>
       <c r="L37" s="16" t="n"/>
       <c r="M37" s="10" t="inlineStr">
         <is>
@@ -6127,7 +6201,9 @@
         <f>IF(AND(ISNUMBER(H38),ISNUMBER(I38),H38&gt;0),1-I38/H38,"")</f>
         <v/>
       </c>
-      <c r="K38" s="15" t="n"/>
+      <c r="K38" s="15" t="n">
+        <v>294000</v>
+      </c>
       <c r="L38" s="16" t="n"/>
       <c r="M38" s="10" t="inlineStr">
         <is>
@@ -6182,7 +6258,9 @@
         <f>IF(AND(ISNUMBER(H39),ISNUMBER(I39),H39&gt;0),1-I39/H39,"")</f>
         <v/>
       </c>
-      <c r="K39" s="15" t="n"/>
+      <c r="K39" s="15" t="n">
+        <v>170000</v>
+      </c>
       <c r="L39" s="16" t="n"/>
       <c r="M39" s="10" t="inlineStr">
         <is>
@@ -6237,7 +6315,9 @@
         <f>IF(AND(ISNUMBER(H40),ISNUMBER(I40),H40&gt;0),1-I40/H40,"")</f>
         <v/>
       </c>
-      <c r="K40" s="15" t="n"/>
+      <c r="K40" s="15" t="n">
+        <v>252000</v>
+      </c>
       <c r="L40" s="16" t="n"/>
       <c r="M40" s="10" t="inlineStr">
         <is>
@@ -6292,7 +6372,9 @@
         <f>IF(AND(ISNUMBER(H41),ISNUMBER(I41),H41&gt;0),1-I41/H41,"")</f>
         <v/>
       </c>
-      <c r="K41" s="15" t="n"/>
+      <c r="K41" s="15" t="n">
+        <v>250000</v>
+      </c>
       <c r="L41" s="16" t="n"/>
       <c r="M41" s="10" t="inlineStr">
         <is>
@@ -6439,24 +6521,28 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>Peugeot 206 RC 2.0 177ch - Bleu Récif</t>
+          <t>206 rc</t>
         </is>
       </c>
       <c r="C2" s="12" t="n">
-        <v>5300</v>
+        <v>5900</v>
       </c>
       <c r="D2" s="12" t="n">
-        <v>9650</v>
+        <v>10600</v>
       </c>
       <c r="E2" s="13">
         <f>IF(AND(ISNUMBER(C2),ISNUMBER(D2),D2&gt;0),1-C2/D2,"")</f>
         <v/>
       </c>
-      <c r="F2" s="15" t="n"/>
-      <c r="G2" s="16" t="n"/>
+      <c r="F2" s="15" t="n">
+        <v>159000</v>
+      </c>
+      <c r="G2" s="16" t="n">
+        <v>2003</v>
+      </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>Belley</t>
+          <t>Tulle</t>
         </is>
       </c>
       <c r="I2" s="19" t="inlineStr">
@@ -6476,24 +6562,28 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Peugeot 206 RC</t>
+          <t>206 rc line 1.6 110 cv</t>
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>5400</v>
+        <v>6800</v>
       </c>
       <c r="D3" s="12" t="n">
-        <v>9650</v>
+        <v>11950</v>
       </c>
       <c r="E3" s="13">
         <f>IF(AND(ISNUMBER(C3),ISNUMBER(D3),D3&gt;0),1-C3/D3,"")</f>
         <v/>
       </c>
-      <c r="F3" s="15" t="n"/>
-      <c r="G3" s="16" t="n"/>
+      <c r="F3" s="15" t="n">
+        <v>124000</v>
+      </c>
+      <c r="G3" s="16" t="n">
+        <v>2006</v>
+      </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>La Roche-sur-Foron</t>
+          <t>Cernay</t>
         </is>
       </c>
       <c r="I3" s="19" t="inlineStr">
@@ -6513,24 +6603,28 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>206 rc</t>
+          <t>Peugeot 206 RC 2.0 177ch - Bleu Récif</t>
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>5900</v>
+        <v>5300</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>9650</v>
+        <v>7680</v>
       </c>
       <c r="E4" s="13">
         <f>IF(AND(ISNUMBER(C4),ISNUMBER(D4),D4&gt;0),1-C4/D4,"")</f>
         <v/>
       </c>
-      <c r="F4" s="15" t="n"/>
-      <c r="G4" s="16" t="n"/>
+      <c r="F4" s="15" t="n">
+        <v>234000</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>2003</v>
+      </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>Tulle</t>
+          <t>Belley</t>
         </is>
       </c>
       <c r="I4" s="19" t="inlineStr">
@@ -6554,20 +6648,24 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>5900</v>
+        <v>6200</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>9650</v>
+        <v>8400</v>
       </c>
       <c r="E5" s="13">
         <f>IF(AND(ISNUMBER(C5),ISNUMBER(D5),D5&gt;0),1-C5/D5,"")</f>
         <v/>
       </c>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="16" t="n"/>
+      <c r="F5" s="15" t="n">
+        <v>215500</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>2005</v>
+      </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>Lons-le-Saunier</t>
+          <t>Coulonges-sur-Sarthe</t>
         </is>
       </c>
       <c r="I5" s="19" t="inlineStr">
@@ -6587,24 +6685,28 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>206 rc</t>
+          <t>Peugeot 206 RC</t>
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>6000</v>
+        <v>5400</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>9650</v>
+        <v>7290</v>
       </c>
       <c r="E6" s="13">
         <f>IF(AND(ISNUMBER(C6),ISNUMBER(D6),D6&gt;0),1-C6/D6,"")</f>
         <v/>
       </c>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="16" t="n"/>
+      <c r="F6" s="15" t="n">
+        <v>244000</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>2003</v>
+      </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>La Côte-Saint-André</t>
+          <t>La Roche-sur-Foron</t>
         </is>
       </c>
       <c r="I6" s="19" t="inlineStr">
